--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-1.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0505883B-0EC5-4315-93CF-5964E9945743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B794DFC4-FD10-4AB9-BB0C-ED60E70F079E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{61690421-D67F-4C5B-B498-34D49E32342A}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{5E0D5A65-3947-49C1-ABA0-7230F9B61F94}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="87" r:id="rId3"/>
+    <pivotCache cacheId="119" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576875347222" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{10FB8E99-7EB9-4D20-9365-33DCC84A9DA8}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579448032404" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{9AF6675A-2456-49DF-BB4B-EED7DE46CCF0}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="Source"/>
   </cacheSource>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5262DB41-E9F3-446D-879F-53DD77312E13}" name="AllErrorPivot" cacheId="87" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E29C02BB-6CD3-47F7-BC95-D96562471B1F}" name="AllErrorPivot" cacheId="119" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -567,7 +567,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7929D629-0F06-477E-9714-8EF1D8F69D2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6E26EF8-7569-4CB7-9883-91D35F2AB3C7}">
   <dimension ref="A4:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -605,7 +605,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A062555-3C2F-4ED1-AE75-2FF3CF4A943C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A4B56C-F5E1-4524-8E07-710B26AC872F}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
